--- a/test_case/test.xlsx
+++ b/test_case/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19560" windowHeight="17520"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>用例ID</t>
   </si>
   <si>
     <t>模块</t>
+  </si>
+  <si>
+    <t>上下文</t>
   </si>
   <si>
     <t>用户输入</t>
@@ -1063,10 +1066,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:5">
+    <row r="1" ht="28.8" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1082,90 +1085,98 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="100.8" spans="1:5">
+    <row r="2" ht="100.8" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" ht="129.6" spans="1:5">
+    <row r="3" ht="129.6" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="4" ht="144" spans="1:5">
+    <row r="4" ht="144" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" ht="129.6" spans="1:5">
+    <row r="5" ht="129.6" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" ht="115.2" spans="1:5">
+    <row r="6" ht="115.2" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>29</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
